--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_depmenores_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_depmenores_a_2022.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:34</t>
+    <t xml:space="preserve">2026-09-24 01:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -540,10 +540,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -554,10 +554,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -568,10 +568,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -582,10 +582,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -596,10 +596,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -613,7 +613,7 @@
         <v>0.09</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8">
@@ -624,10 +624,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -641,7 +641,7 @@
         <v>0.1</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -652,10 +652,10 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         <v>0.03</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12">
@@ -683,7 +683,7 @@
         <v>0.14</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13">
@@ -697,7 +697,7 @@
         <v>0.13</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14">
@@ -708,10 +708,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15">
@@ -722,10 +722,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
@@ -739,7 +739,7 @@
         <v>-0.26</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17">
@@ -753,7 +753,7 @@
         <v>-0.22</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18">
@@ -767,7 +767,7 @@
         <v>-0.23</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19">
@@ -778,10 +778,10 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20">
@@ -792,10 +792,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21">
@@ -806,10 +806,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -820,10 +820,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         <v>0.14</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_depmenores_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_depmenores_a_2022.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:24</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_depmenores_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_depmenores_a_2022.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
